--- a/artfynd/A 24727-2026 artfynd.xlsx
+++ b/artfynd/A 24727-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123317801</v>
+        <v>123856271</v>
       </c>
       <c r="B2" t="n">
-        <v>95323</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393999</v>
+        <v>393935</v>
       </c>
       <c r="R2" t="n">
-        <v>6504375</v>
+        <v>6504313</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,76 +765,69 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Avverknngsanmäld barrskog med hällmarker</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123317808</v>
+        <v>123317801</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>393947</v>
+        <v>393999</v>
       </c>
       <c r="R3" t="n">
-        <v>6504308</v>
+        <v>6504375</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,76 +879,55 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123317822</v>
+        <v>123856275</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>393947</v>
+        <v>393991</v>
       </c>
       <c r="R4" t="n">
-        <v>6504225</v>
+        <v>6504398</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,88 +965,71 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Avverknngsanmäld barrskog med hällmarker</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123317810</v>
+        <v>123856267</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394012</v>
+        <v>393959</v>
       </c>
       <c r="R5" t="n">
-        <v>6504408</v>
+        <v>6504224</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,38 +1067,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Avverknngsanmäld barrskog med hällmarker</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Skogsgruppen Skaraborg</t>
-        </is>
-      </c>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123856267</v>
+        <v>123317808</v>
       </c>
       <c r="B6" t="n">
-        <v>91413</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,37 +1101,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>393959</v>
+        <v>393947</v>
       </c>
       <c r="R6" t="n">
-        <v>6504224</v>
+        <v>6504308</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,74 +1179,80 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Avverknngsanmäld barrskog med hällmarker</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123856275</v>
+        <v>123317810</v>
       </c>
       <c r="B7" t="n">
-        <v>95345</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Otterstad 1:7, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>393991</v>
+        <v>394012</v>
       </c>
       <c r="R7" t="n">
-        <v>6504398</v>
+        <v>6504408</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,73 +1290,69 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Avverknngsanmäld barrskog med hällmarker</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123856271</v>
+        <v>123317822</v>
       </c>
       <c r="B8" t="n">
-        <v>91282</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,13 +1360,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>393935</v>
+        <v>393947</v>
       </c>
       <c r="R8" t="n">
-        <v>6504313</v>
+        <v>6504225</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,23 +1408,136 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Avverknngsanmäld barrskog med hällmarker</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Ada  Arenander, Liselotte Larsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123317825</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Otterstad 1:7, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>394022</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6504439</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Otterstad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24727-2026 artfynd.xlsx
+++ b/artfynd/A 24727-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123856271</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123317801</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123856275</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123856267</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123317808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123317810</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123317822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,8 +1578,23 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123317825</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>